--- a/base/pacotes/thozen-electra/preliminar-thozen-electra.xlsx
+++ b/base/pacotes/thozen-electra/preliminar-thozen-electra.xlsx
@@ -645,7 +645,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Gerado em 2026-04-14T07:44:00 | AC=37894 m² | UR=348 | padrão=alto | 5 projetos similares de referência</t>
+          <t>Gerado em 2026-04-14T08:53:59 | AC=37894 m² | UR=348 | padrão=alto | 5 projetos similares de referência</t>
         </is>
       </c>
     </row>
@@ -718,13 +718,13 @@
         </is>
       </c>
       <c r="C5" s="7" t="n">
-        <v>22703745.2546</v>
+        <v>24267626.0949</v>
       </c>
       <c r="D5" s="8" t="n">
-        <v>599.14</v>
+        <v>640.41</v>
       </c>
       <c r="E5" s="9" t="n">
-        <v>0.139514887775858</v>
+        <v>0.1541021476267822</v>
       </c>
       <c r="F5" s="5" t="n">
         <v>2</v>
@@ -733,16 +733,16 @@
         <v>541992.03</v>
       </c>
       <c r="H5" s="9" t="n">
-        <v>0.02387236219936828</v>
+        <v>0.02233395338631426</v>
       </c>
       <c r="I5" s="5" t="inlineStr">
         <is>
-          <t>calibrado (n=7)</t>
+          <t>calibrado (n=22)</t>
         </is>
       </c>
       <c r="J5" s="5" t="inlineStr">
         <is>
-          <t>538–1443</t>
+          <t>438–3120</t>
         </is>
       </c>
     </row>
@@ -756,13 +756,13 @@
         </is>
       </c>
       <c r="C6" s="7" t="n">
-        <v>4901953.610400001</v>
+        <v>4706042.1991</v>
       </c>
       <c r="D6" s="8" t="n">
-        <v>129.36</v>
+        <v>124.19</v>
       </c>
       <c r="E6" s="9" t="n">
-        <v>0.0301225855103732</v>
+        <v>0.02988389580701438</v>
       </c>
       <c r="F6" s="5" t="n">
         <v>4</v>
@@ -771,16 +771,16 @@
         <v>349282.29</v>
       </c>
       <c r="H6" s="9" t="n">
-        <v>0.07125369143823833</v>
+        <v>0.07421996557251398</v>
       </c>
       <c r="I6" s="5" t="inlineStr">
         <is>
-          <t>calibrado (n=8)</t>
+          <t>calibrado (n=23)</t>
         </is>
       </c>
       <c r="J6" s="5" t="inlineStr">
         <is>
-          <t>41–207</t>
+          <t>65–899</t>
         </is>
       </c>
     </row>
@@ -794,13 +794,13 @@
         </is>
       </c>
       <c r="C7" s="7" t="n">
-        <v>8265036.3479</v>
+        <v>8730752.256000001</v>
       </c>
       <c r="D7" s="8" t="n">
-        <v>218.11</v>
+        <v>230.4</v>
       </c>
       <c r="E7" s="9" t="n">
-        <v>0.05078878421202457</v>
+        <v>0.05544125609095833</v>
       </c>
       <c r="F7" s="5" t="n">
         <v>10</v>
@@ -809,16 +809,16 @@
         <v>1545224.52</v>
       </c>
       <c r="H7" s="9" t="n">
-        <v>0.1869591923080428</v>
+        <v>0.1769864124752917</v>
       </c>
       <c r="I7" s="5" t="inlineStr">
         <is>
-          <t>calibrado (n=8)</t>
+          <t>calibrado (n=23)</t>
         </is>
       </c>
       <c r="J7" s="5" t="inlineStr">
         <is>
-          <t>142–318</t>
+          <t>149–1392</t>
         </is>
       </c>
     </row>
@@ -832,13 +832,13 @@
         </is>
       </c>
       <c r="C8" s="7" t="n">
-        <v>27878534.873</v>
+        <v>27216907.5536</v>
       </c>
       <c r="D8" s="8" t="n">
-        <v>735.7</v>
+        <v>718.24</v>
       </c>
       <c r="E8" s="9" t="n">
-        <v>0.1713140550400553</v>
+        <v>0.1728304156891055</v>
       </c>
       <c r="F8" s="5" t="n">
         <v>27</v>
@@ -847,16 +847,16 @@
         <v>12297697.99</v>
       </c>
       <c r="H8" s="9" t="n">
-        <v>0.4411170833051977</v>
+        <v>0.4518403850908247</v>
       </c>
       <c r="I8" s="5" t="inlineStr">
         <is>
-          <t>calibrado (n=8)</t>
+          <t>calibrado (n=23)</t>
         </is>
       </c>
       <c r="J8" s="5" t="inlineStr">
         <is>
-          <t>293–1034</t>
+          <t>568–4381</t>
         </is>
       </c>
     </row>
@@ -870,13 +870,13 @@
         </is>
       </c>
       <c r="C9" s="7" t="n">
-        <v>7638271.4073</v>
+        <v>6892898.591</v>
       </c>
       <c r="D9" s="8" t="n">
-        <v>201.57</v>
+        <v>181.9</v>
       </c>
       <c r="E9" s="9" t="n">
-        <v>0.04693730334976751</v>
+        <v>0.04377067917945016</v>
       </c>
       <c r="F9" s="5" t="n">
         <v>10</v>
@@ -885,16 +885,16 @@
         <v>244639.39</v>
       </c>
       <c r="H9" s="9" t="n">
-        <v>0.03202810910413511</v>
+        <v>0.03549151155646241</v>
       </c>
       <c r="I9" s="5" t="inlineStr">
         <is>
-          <t>calibrado (n=8)</t>
+          <t>calibrado (n=21)</t>
         </is>
       </c>
       <c r="J9" s="5" t="inlineStr">
         <is>
-          <t>134–319</t>
+          <t>93–319</t>
         </is>
       </c>
     </row>
@@ -908,13 +908,13 @@
         </is>
       </c>
       <c r="C10" s="7" t="n">
-        <v>3532847.3647</v>
+        <v>2817410.7215</v>
       </c>
       <c r="D10" s="8" t="n">
-        <v>93.23</v>
+        <v>74.34999999999999</v>
       </c>
       <c r="E10" s="9" t="n">
-        <v>0.02170940512625304</v>
+        <v>0.0178908740901161</v>
       </c>
       <c r="F10" s="5" t="n">
         <v>6</v>
@@ -923,16 +923,16 @@
         <v>121349.52</v>
       </c>
       <c r="H10" s="9" t="n">
-        <v>0.03434892806649876</v>
+        <v>0.04307129204626334</v>
       </c>
       <c r="I10" s="5" t="inlineStr">
         <is>
-          <t>calibrado (n=7)</t>
+          <t>calibrado (n=20)</t>
         </is>
       </c>
       <c r="J10" s="5" t="inlineStr">
         <is>
-          <t>42–274</t>
+          <t>44–1361</t>
         </is>
       </c>
     </row>
@@ -946,13 +946,13 @@
         </is>
       </c>
       <c r="C11" s="7" t="n">
-        <v>15224249.2464</v>
+        <v>12130971.0057</v>
       </c>
       <c r="D11" s="8" t="n">
-        <v>401.76</v>
+        <v>320.13</v>
       </c>
       <c r="E11" s="9" t="n">
-        <v>0.09355326186338539</v>
+        <v>0.07703302652950732</v>
       </c>
       <c r="F11" s="5" t="n">
         <v>30</v>
@@ -961,16 +961,16 @@
         <v>5101674.38</v>
       </c>
       <c r="H11" s="9" t="n">
-        <v>0.3351018692239532</v>
+        <v>0.4205495485565721</v>
       </c>
       <c r="I11" s="5" t="inlineStr">
         <is>
-          <t>calibrado (n=7)</t>
+          <t>calibrado (n=21)</t>
         </is>
       </c>
       <c r="J11" s="5" t="inlineStr">
         <is>
-          <t>210–598</t>
+          <t>168–2068</t>
         </is>
       </c>
     </row>
@@ -990,7 +990,7 @@
         <v>211.02</v>
       </c>
       <c r="E12" s="9" t="n">
-        <v>0.04913781690166166</v>
+        <v>0.05077783793539073</v>
       </c>
       <c r="F12" s="5" t="n">
         <v>25</v>
@@ -1003,12 +1003,12 @@
       </c>
       <c r="I12" s="5" t="inlineStr">
         <is>
-          <t>calibrado (n=7)</t>
+          <t>calibrado (n=21)</t>
         </is>
       </c>
       <c r="J12" s="5" t="inlineStr">
         <is>
-          <t>100–325</t>
+          <t>74–594</t>
         </is>
       </c>
     </row>
@@ -1022,13 +1022,13 @@
         </is>
       </c>
       <c r="C13" s="7" t="n">
-        <v>1664299.6488</v>
+        <v>1372137.7569</v>
       </c>
       <c r="D13" s="8" t="n">
-        <v>43.92</v>
+        <v>36.21</v>
       </c>
       <c r="E13" s="9" t="n">
-        <v>0.01022714869832708</v>
+        <v>0.008713228659086808</v>
       </c>
       <c r="F13" s="5" t="n">
         <v>0</v>
@@ -1041,12 +1041,12 @@
       </c>
       <c r="I13" s="5" t="inlineStr">
         <is>
-          <t>calibrado (n=3)</t>
+          <t>calibrado (n=9)</t>
         </is>
       </c>
       <c r="J13" s="5" t="inlineStr">
         <is>
-          <t>34–213</t>
+          <t>24–125</t>
         </is>
       </c>
     </row>
@@ -1060,13 +1060,13 @@
         </is>
       </c>
       <c r="C14" s="7" t="n">
-        <v>4620859.7658912</v>
+        <v>3108056.8578</v>
       </c>
       <c r="D14" s="8" t="n">
-        <v>121.94208</v>
+        <v>82.02</v>
       </c>
       <c r="E14" s="9" t="n">
-        <v>0.02839525921546667</v>
+        <v>0.01973650965529688</v>
       </c>
       <c r="F14" s="5" t="n">
         <v>5</v>
@@ -1075,16 +1075,16 @@
         <v>165049.38</v>
       </c>
       <c r="H14" s="9" t="n">
-        <v>0.03571832696986593</v>
+        <v>0.0531037196394239</v>
       </c>
       <c r="I14" s="5" t="inlineStr">
         <is>
-          <t>calibrado (n=61)</t>
+          <t>calibrado (n=12)</t>
         </is>
       </c>
       <c r="J14" s="5" t="inlineStr">
         <is>
-          <t>38–899</t>
+          <t>38–1217</t>
         </is>
       </c>
     </row>
@@ -1098,13 +1098,13 @@
         </is>
       </c>
       <c r="C15" s="7" t="n">
-        <v>2389967.6423</v>
+        <v>2358136.7747</v>
       </c>
       <c r="D15" s="8" t="n">
-        <v>63.07</v>
+        <v>62.23</v>
       </c>
       <c r="E15" s="9" t="n">
-        <v>0.01468639044634537</v>
+        <v>0.01497443301449799</v>
       </c>
       <c r="F15" s="5" t="n">
         <v>5</v>
@@ -1113,16 +1113,16 @@
         <v>648293.71</v>
       </c>
       <c r="H15" s="9" t="n">
-        <v>0.2712562708071272</v>
+        <v>0.2749177727752773</v>
       </c>
       <c r="I15" s="5" t="inlineStr">
         <is>
-          <t>calibrado (n=7)</t>
+          <t>calibrado (n=12)</t>
         </is>
       </c>
       <c r="J15" s="5" t="inlineStr">
         <is>
-          <t>1–85</t>
+          <t>34–92</t>
         </is>
       </c>
     </row>
@@ -1136,13 +1136,13 @@
         </is>
       </c>
       <c r="C16" s="7" t="n">
-        <v>12403428.0748</v>
+        <v>8982746.624500001</v>
       </c>
       <c r="D16" s="8" t="n">
-        <v>327.32</v>
+        <v>237.05</v>
       </c>
       <c r="E16" s="9" t="n">
-        <v>0.07621926939745945</v>
+        <v>0.05704144859531975</v>
       </c>
       <c r="F16" s="5" t="n">
         <v>30</v>
@@ -1151,16 +1151,16 @@
         <v>3566798.48</v>
       </c>
       <c r="H16" s="9" t="n">
-        <v>0.287565539017931</v>
+        <v>0.3970721460930148</v>
       </c>
       <c r="I16" s="5" t="inlineStr">
         <is>
-          <t>calibrado (n=7)</t>
+          <t>calibrado (n=16)</t>
         </is>
       </c>
       <c r="J16" s="5" t="inlineStr">
         <is>
-          <t>189–638</t>
+          <t>166–2815</t>
         </is>
       </c>
     </row>
@@ -1174,13 +1174,13 @@
         </is>
       </c>
       <c r="C17" s="7" t="n">
-        <v>5449520.3209</v>
+        <v>6031191.5324</v>
       </c>
       <c r="D17" s="8" t="n">
-        <v>143.81</v>
+        <v>159.16</v>
       </c>
       <c r="E17" s="9" t="n">
-        <v>0.03348739194686742</v>
+        <v>0.03829874270588943</v>
       </c>
       <c r="F17" s="5" t="n">
         <v>14</v>
@@ -1189,16 +1189,16 @@
         <v>92863.95</v>
       </c>
       <c r="H17" s="9" t="n">
-        <v>0.01704075671465031</v>
+        <v>0.01539728086914967</v>
       </c>
       <c r="I17" s="5" t="inlineStr">
         <is>
-          <t>calibrado (n=7)</t>
+          <t>calibrado (n=16)</t>
         </is>
       </c>
       <c r="J17" s="5" t="inlineStr">
         <is>
-          <t>107–252</t>
+          <t>87–2883</t>
         </is>
       </c>
     </row>
@@ -1212,13 +1212,13 @@
         </is>
       </c>
       <c r="C18" s="7" t="n">
-        <v>14817647.8067</v>
+        <v>14986654.5561</v>
       </c>
       <c r="D18" s="8" t="n">
-        <v>391.03</v>
+        <v>395.49</v>
       </c>
       <c r="E18" s="9" t="n">
-        <v>0.09105468933303362</v>
+        <v>0.09516693737592494</v>
       </c>
       <c r="F18" s="5" t="n">
         <v>19</v>
@@ -1227,16 +1227,16 @@
         <v>19235216.6</v>
       </c>
       <c r="H18" s="9" t="n">
-        <v>1.298128883270025</v>
+        <v>1.283489689309661</v>
       </c>
       <c r="I18" s="5" t="inlineStr">
         <is>
-          <t>calibrado (n=8)</t>
+          <t>calibrado (n=23)</t>
         </is>
       </c>
       <c r="J18" s="5" t="inlineStr">
         <is>
-          <t>267–586</t>
+          <t>260–1896</t>
         </is>
       </c>
     </row>
@@ -1250,13 +1250,13 @@
         </is>
       </c>
       <c r="C19" s="7" t="n">
-        <v>2637414.744</v>
+        <v>5380174.5022</v>
       </c>
       <c r="D19" s="8" t="n">
-        <v>69.59999999999999</v>
+        <v>141.98</v>
       </c>
       <c r="E19" s="9" t="n">
-        <v>0.01620695695363307</v>
+        <v>0.03416471154424593</v>
       </c>
       <c r="F19" s="5" t="n">
         <v>11</v>
@@ -1265,16 +1265,16 @@
         <v>911727.83</v>
       </c>
       <c r="H19" s="9" t="n">
-        <v>0.3456899723769801</v>
+        <v>0.1694606428894056</v>
       </c>
       <c r="I19" s="5" t="inlineStr">
         <is>
-          <t>calibrado (n=6)</t>
+          <t>calibrado (n=17)</t>
         </is>
       </c>
       <c r="J19" s="5" t="inlineStr">
         <is>
-          <t>33–209</t>
+          <t>38–414</t>
         </is>
       </c>
     </row>
@@ -1288,13 +1288,13 @@
         </is>
       </c>
       <c r="C20" s="7" t="n">
-        <v>7934980.566</v>
+        <v>7831530.2463</v>
       </c>
       <c r="D20" s="8" t="n">
-        <v>209.4</v>
+        <v>206.67</v>
       </c>
       <c r="E20" s="9" t="n">
-        <v>0.04876058600705123</v>
+        <v>0.04973109547013175</v>
       </c>
       <c r="F20" s="5" t="n">
         <v>1</v>
@@ -1303,16 +1303,16 @@
         <v>129392.06</v>
       </c>
       <c r="H20" s="9" t="n">
-        <v>0.01630653773172707</v>
+        <v>0.01652193836078603</v>
       </c>
       <c r="I20" s="5" t="inlineStr">
         <is>
-          <t>calibrado (n=6)</t>
+          <t>calibrado (n=10)</t>
         </is>
       </c>
       <c r="J20" s="5" t="inlineStr">
         <is>
-          <t>142–323</t>
+          <t>84–538</t>
         </is>
       </c>
     </row>
@@ -1332,7 +1332,7 @@
         <v>262.06</v>
       </c>
       <c r="E21" s="9" t="n">
-        <v>0.06102291866765924</v>
+        <v>0.06305961619442942</v>
       </c>
       <c r="F21" s="5" t="n">
         <v>30</v>
@@ -1345,12 +1345,12 @@
       </c>
       <c r="I21" s="5" t="inlineStr">
         <is>
-          <t>calibrado (n=7)</t>
+          <t>calibrado (n=15)</t>
         </is>
       </c>
       <c r="J21" s="5" t="inlineStr">
         <is>
-          <t>70–991</t>
+          <t>70–3836</t>
         </is>
       </c>
     </row>
@@ -1364,13 +1364,13 @@
         </is>
       </c>
       <c r="C22" s="7" t="n">
-        <v>2743896.5749</v>
+        <v>2737454.6136</v>
       </c>
       <c r="D22" s="8" t="n">
-        <v>72.41</v>
+        <v>72.23999999999999</v>
       </c>
       <c r="E22" s="9" t="n">
-        <v>0.01686128955477832</v>
+        <v>0.01738314383685256</v>
       </c>
       <c r="F22" s="5" t="n">
         <v>0</v>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="J22" s="5" t="inlineStr">
         <is>
-          <t>43–81</t>
+          <t>34–81</t>
         </is>
       </c>
     </row>
@@ -1399,10 +1399,10 @@
         </is>
       </c>
       <c r="C23" s="11" t="n">
-        <v>162733494.7297912</v>
+        <v>157477533.3675</v>
       </c>
       <c r="D23" s="12" t="n">
-        <v>4294.452079999999</v>
+        <v>4155.749999999999</v>
       </c>
       <c r="E23" s="13" t="n">
         <v>1</v>
@@ -1411,7 +1411,7 @@
         <v>45963582.05</v>
       </c>
       <c r="H23" s="13" t="n">
-        <v>0.2824469672105283</v>
+        <v>0.2918739014201877</v>
       </c>
     </row>
     <row r="25">
@@ -1489,7 +1489,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Total calibrado V2 (mediana de 3 refs): R$ 1.664.300  |  R$/m²: 43.92</t>
+          <t>Total calibrado V2 (mediana de 9 refs): R$ 1.372.138  |  R$/m²: 36.21</t>
         </is>
       </c>
     </row>
@@ -1590,7 +1590,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Total calibrado V2 (mediana de 61 refs): R$ 4.620.860  |  R$/m²: 93.80</t>
+          <t>Total calibrado V2 (mediana de 12 refs): R$ 3.108.057  |  R$/m²: 82.02</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
         </is>
       </c>
       <c r="F12" s="27" t="n">
-        <v>0.03571832750493951</v>
+        <v>0.05310372043493702</v>
       </c>
     </row>
   </sheetData>
@@ -1863,7 +1863,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Total calibrado V2 (mediana de 7 refs): R$ 2.389.968  |  R$/m²: 63.07</t>
+          <t>Total calibrado V2 (mediana de 12 refs): R$ 2.358.137  |  R$/m²: 62.23</t>
         </is>
       </c>
     </row>
@@ -2093,7 +2093,7 @@
         </is>
       </c>
       <c r="F12" s="27" t="n">
-        <v>0.2712562719075605</v>
+        <v>0.2749177738905647</v>
       </c>
     </row>
   </sheetData>
@@ -2136,7 +2136,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Total calibrado V2 (mediana de 7 refs): R$ 12.403.428  |  R$/m²: 327.32</t>
+          <t>Total calibrado V2 (mediana de 16 refs): R$ 8.982.747  |  R$/m²: 237.05</t>
         </is>
       </c>
     </row>
@@ -3166,7 +3166,7 @@
         </is>
       </c>
       <c r="F37" s="27" t="n">
-        <v>0.2875655386743365</v>
+        <v>0.3970721456185776</v>
       </c>
     </row>
   </sheetData>
@@ -3209,7 +3209,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Total calibrado V2 (mediana de 7 refs): R$ 5.449.520  |  R$/m²: 143.81</t>
+          <t>Total calibrado V2 (mediana de 16 refs): R$ 6.031.192  |  R$/m²: 159.16</t>
         </is>
       </c>
     </row>
@@ -3727,7 +3727,7 @@
         </is>
       </c>
       <c r="F21" s="27" t="n">
-        <v>0.01704075731672165</v>
+        <v>0.01539728141315494</v>
       </c>
     </row>
   </sheetData>
@@ -3770,7 +3770,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Total calibrado V2 (mediana de 8 refs): R$ 14.817.648  |  R$/m²: 391.03</t>
+          <t>Total calibrado V2 (mediana de 23 refs): R$ 14.986.655  |  R$/m²: 395.49</t>
         </is>
       </c>
     </row>
@@ -4448,7 +4448,7 @@
         </is>
       </c>
       <c r="F26" s="27" t="n">
-        <v>1.298128883389476</v>
+        <v>1.283489689427765</v>
       </c>
     </row>
   </sheetData>
@@ -4491,7 +4491,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Total calibrado V2 (mediana de 6 refs): R$ 2.637.415  |  R$/m²: 69.60</t>
+          <t>Total calibrado V2 (mediana de 17 refs): R$ 5.380.175  |  R$/m²: 141.98</t>
         </is>
       </c>
     </row>
@@ -4913,7 +4913,7 @@
         </is>
       </c>
       <c r="F18" s="27" t="n">
-        <v>0.3456899723769801</v>
+        <v>0.1694606428894057</v>
       </c>
     </row>
   </sheetData>
@@ -4956,7 +4956,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Total calibrado V2 (mediana de 6 refs): R$ 7.934.981  |  R$/m²: 209.40</t>
+          <t>Total calibrado V2 (mediana de 10 refs): R$ 7.831.530  |  R$/m²: 206.67</t>
         </is>
       </c>
     </row>
@@ -5058,7 +5058,7 @@
         </is>
       </c>
       <c r="F8" s="27" t="n">
-        <v>0.01630653740708859</v>
+        <v>0.01652193803185925</v>
       </c>
     </row>
   </sheetData>
@@ -5101,7 +5101,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Total calibrado V2 (mediana de 7 refs): R$ 9.930.473  |  R$/m²: 262.06</t>
+          <t>Total calibrado V2 (mediana de 15 refs): R$ 9.930.473  |  R$/m²: 262.06</t>
         </is>
       </c>
     </row>
@@ -6066,7 +6066,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Total calibrado V2 (mediana de 7 refs): R$ 2.743.897  |  R$/m²: 72.41</t>
+          <t>Total calibrado V2 (mediana de 7 refs): R$ 2.737.455  |  R$/m²: 72.24</t>
         </is>
       </c>
     </row>
@@ -6167,7 +6167,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Total calibrado V2 (mediana de 7 refs): R$ 22.703.745  |  R$/m²: 599.14</t>
+          <t>Total calibrado V2 (mediana de 22 refs): R$ 24.267.626  |  R$/m²: 640.41</t>
         </is>
       </c>
     </row>
@@ -6301,7 +6301,7 @@
         </is>
       </c>
       <c r="F9" s="27" t="n">
-        <v>0.02387236219936828</v>
+        <v>0.02233395338631426</v>
       </c>
     </row>
   </sheetData>
@@ -7168,7 +7168,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Total calibrado V2 (mediana de 8 refs): R$ 4.901.954  |  R$/m²: 129.36</t>
+          <t>Total calibrado V2 (mediana de 23 refs): R$ 4.706.042  |  R$/m²: 124.19</t>
         </is>
       </c>
     </row>
@@ -7366,7 +7366,7 @@
         </is>
       </c>
       <c r="F11" s="27" t="n">
-        <v>0.07125369241743977</v>
+        <v>0.07421996659247934</v>
       </c>
     </row>
   </sheetData>
@@ -7409,7 +7409,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Total calibrado V2 (mediana de 8 refs): R$ 8.265.036  |  R$/m²: 218.11</t>
+          <t>Total calibrado V2 (mediana de 23 refs): R$ 8.730.752  |  R$/m²: 230.40</t>
         </is>
       </c>
     </row>
@@ -7799,7 +7799,7 @@
         </is>
       </c>
       <c r="F17" s="27" t="n">
-        <v>0.1869591928104</v>
+        <v>0.1769864129508522</v>
       </c>
     </row>
   </sheetData>
@@ -7842,7 +7842,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Total calibrado V2 (mediana de 8 refs): R$ 27.878.535  |  R$/m²: 735.70</t>
+          <t>Total calibrado V2 (mediana de 23 refs): R$ 27.216.908  |  R$/m²: 718.24</t>
         </is>
       </c>
     </row>
@@ -8776,7 +8776,7 @@
         </is>
       </c>
       <c r="F34" s="27" t="n">
-        <v>0.4411170834081083</v>
+        <v>0.451840385196237</v>
       </c>
     </row>
   </sheetData>
@@ -8819,7 +8819,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Total calibrado V2 (mediana de 8 refs): R$ 7.638.271  |  R$/m²: 201.57</t>
+          <t>Total calibrado V2 (mediana de 21 refs): R$ 6.892.899  |  R$/m²: 181.90</t>
         </is>
       </c>
     </row>
@@ -9209,7 +9209,7 @@
         </is>
       </c>
       <c r="F17" s="27" t="n">
-        <v>0.03202810891043945</v>
+        <v>0.03549151134182121</v>
       </c>
     </row>
   </sheetData>
@@ -9252,7 +9252,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Total calibrado V2 (mediana de 7 refs): R$ 3.532.847  |  R$/m²: 93.23</t>
+          <t>Total calibrado V2 (mediana de 20 refs): R$ 2.817.411  |  R$/m²: 74.35</t>
         </is>
       </c>
     </row>
@@ -9514,7 +9514,7 @@
         </is>
       </c>
       <c r="F13" s="27" t="n">
-        <v>0.03434892671631305</v>
+        <v>0.04307129035321945</v>
       </c>
     </row>
   </sheetData>
@@ -9557,7 +9557,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Total calibrado V2 (mediana de 7 refs): R$ 15.224.249  |  R$/m²: 401.76</t>
+          <t>Total calibrado V2 (mediana de 21 refs): R$ 12.130.971  |  R$/m²: 320.13</t>
         </is>
       </c>
     </row>
@@ -10587,7 +10587,7 @@
         </is>
       </c>
       <c r="F37" s="27" t="n">
-        <v>0.3351018695071855</v>
+        <v>0.4205495489120259</v>
       </c>
     </row>
   </sheetData>
@@ -10630,7 +10630,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Total calibrado V2 (mediana de 7 refs): R$ 7.996.369  |  R$/m²: 211.02</t>
+          <t>Total calibrado V2 (mediana de 21 refs): R$ 7.996.369  |  R$/m²: 211.02</t>
         </is>
       </c>
     </row>
